--- a/doku/ConnectionListEmobLab.xlsx
+++ b/doku/ConnectionListEmobLab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htlr-my.sharepoint.com/personal/stefan_zudrell-koch_htl-rankweil_at/Documents/4ABHEL/NCT/EMobLab/emLab_base_v1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="8_{1B79ACBD-35DB-4374-A808-23133F7AD195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED9DB8B4-308C-4E91-BEE8-F4482A2BC0AF}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="8_{1B79ACBD-35DB-4374-A808-23133F7AD195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F91B69-E159-45E6-9CF9-E4E5362892D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2CE193C3-0B43-484A-AC25-4C937C58CF5A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="111">
   <si>
     <t>NRF</t>
   </si>
@@ -242,12 +242,6 @@
     <t>AIN0/CLK</t>
   </si>
   <si>
-    <t>AIN5/CLK</t>
-  </si>
-  <si>
-    <t>AIN4/CLK</t>
-  </si>
-  <si>
     <t>SWC</t>
   </si>
   <si>
@@ -296,9 +290,6 @@
     <t>AIN1</t>
   </si>
   <si>
-    <t>VREGM/AIN2</t>
-  </si>
-  <si>
     <t>AIN3</t>
   </si>
   <si>
@@ -317,9 +308,6 @@
     <t>SWVMG</t>
   </si>
   <si>
-    <t>With this Pin VMSW can be turned on over ExpansionPort</t>
-  </si>
-  <si>
     <t>Interrupt Pin of MC3635</t>
   </si>
   <si>
@@ -335,9 +323,6 @@
     <t>GPIO</t>
   </si>
   <si>
-    <t>GPIO/AIN</t>
-  </si>
-  <si>
     <t>LED</t>
   </si>
   <si>
@@ -351,6 +336,39 @@
   </si>
   <si>
     <t>VTEMP</t>
+  </si>
+  <si>
+    <t>Pinplanner</t>
+  </si>
+  <si>
+    <t>AIN2</t>
+  </si>
+  <si>
+    <t>AIN5</t>
+  </si>
+  <si>
+    <t>AIN4</t>
+  </si>
+  <si>
+    <t>Copy/Paste previous design (JZ)</t>
+  </si>
+  <si>
+    <t>GP0</t>
+  </si>
+  <si>
+    <t>GP1</t>
+  </si>
+  <si>
+    <t>GP2</t>
+  </si>
+  <si>
+    <t>GP3</t>
+  </si>
+  <si>
+    <t>GP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -416,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -435,6 +453,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -750,18 +771,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD24F535-1417-4419-BAEF-078237F805D1}">
-  <dimension ref="D4:N49"/>
+  <dimension ref="D4:P49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="7" width="10.88671875" style="1"/>
+    <col min="4" max="5" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="9" max="10" width="10.88671875" style="1"/>
     <col min="11" max="11" width="16.44140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="23.33203125" style="1" customWidth="1"/>
     <col min="13" max="13" width="10.88671875" style="1"/>
     <col min="14" max="14" width="51.21875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
         <v>17</v>
@@ -775,8 +798,11 @@
       <c r="L4" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D5" s="1">
         <v>1</v>
       </c>
@@ -790,7 +816,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D6" s="1">
         <v>2</v>
       </c>
@@ -810,7 +836,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D7" s="1">
         <v>3</v>
       </c>
@@ -827,13 +853,16 @@
         <v>53</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="4:14" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D8" s="1">
         <v>4</v>
       </c>
@@ -847,7 +876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D9" s="1">
         <v>5</v>
       </c>
@@ -861,7 +890,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D10" s="1">
         <v>6</v>
       </c>
@@ -878,7 +907,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D11" s="1">
         <v>7</v>
       </c>
@@ -886,10 +915,10 @@
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I11" s="1">
         <v>7</v>
@@ -898,10 +927,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="4:14" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D12" s="1">
         <v>8</v>
       </c>
@@ -909,7 +941,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I12" s="1">
         <v>8</v>
@@ -917,17 +949,17 @@
       <c r="J12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>87</v>
+      <c r="K12" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D13" s="1">
         <v>9</v>
       </c>
@@ -935,10 +967,10 @@
         <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I13" s="1">
         <v>9</v>
@@ -947,16 +979,16 @@
         <v>5</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="4:14" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D14" s="1">
         <v>10</v>
       </c>
@@ -964,10 +996,10 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I14" s="1">
         <v>10</v>
@@ -979,7 +1011,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D15" s="1">
         <v>11</v>
       </c>
@@ -987,10 +1019,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I15" s="1">
         <v>11</v>
@@ -999,16 +1031,16 @@
         <v>4</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="4:14" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D16" s="1">
         <v>12</v>
       </c>
@@ -1016,7 +1048,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I16" s="1">
         <v>12</v>
@@ -1028,7 +1060,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D17" s="1">
         <v>13</v>
       </c>
@@ -1036,7 +1068,7 @@
         <v>29</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I17" s="1">
         <v>13</v>
@@ -1051,7 +1083,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D18" s="1">
         <v>14</v>
       </c>
@@ -1059,7 +1091,7 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I18" s="1">
         <v>14</v>
@@ -1068,7 +1100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D19" s="1">
         <v>15</v>
       </c>
@@ -1076,10 +1108,10 @@
         <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I19" s="1">
         <v>15</v>
@@ -1087,14 +1119,14 @@
       <c r="J19" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K19" s="5" t="s">
-        <v>85</v>
+      <c r="K19" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="4:14" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D20" s="1">
         <v>16</v>
       </c>
@@ -1102,10 +1134,10 @@
         <v>31</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I20" s="1">
         <v>16</v>
@@ -1113,8 +1145,9 @@
       <c r="J20" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D21" s="1">
         <v>17</v>
       </c>
@@ -1122,10 +1155,10 @@
         <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I21" s="1">
         <v>17</v>
@@ -1133,14 +1166,14 @@
       <c r="J21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="7" t="s">
         <v>67</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="4:14" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D22" s="1">
         <v>18</v>
       </c>
@@ -1154,10 +1187,13 @@
         <v>63</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="4:14" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D23" s="1">
         <v>19</v>
       </c>
@@ -1165,7 +1201,7 @@
         <v>33</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I23" s="1">
         <v>19</v>
@@ -1174,16 +1210,16 @@
         <v>14</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="4:14" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D24" s="1">
         <v>20</v>
       </c>
@@ -1197,10 +1233,13 @@
         <v>64</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="4:14" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D25" s="1">
         <v>21</v>
       </c>
@@ -1214,16 +1253,16 @@
         <v>65</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="4:14" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D26" s="1">
         <v>22</v>
       </c>
@@ -1237,10 +1276,13 @@
         <v>66</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="4:14" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D27" s="1">
         <v>23</v>
       </c>
@@ -1248,7 +1290,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I27" s="1">
         <v>23</v>
@@ -1257,16 +1299,16 @@
         <v>13</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="4:14" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D28" s="1">
         <v>24</v>
       </c>
@@ -1274,7 +1316,7 @@
         <v>37</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I28" s="1">
         <v>24</v>
@@ -1283,7 +1325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D29" s="1">
         <v>25</v>
       </c>
@@ -1294,10 +1336,10 @@
         <v>25</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="4:14" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D30" s="1">
         <v>26</v>
       </c>
@@ -1314,13 +1356,13 @@
         <v>15</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="4:14" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D31" s="1">
         <v>27</v>
       </c>
@@ -1328,19 +1370,19 @@
         <v>40</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I31" s="1">
         <v>27</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="4:14" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D32" s="1">
         <v>28</v>
       </c>
@@ -1348,10 +1390,10 @@
         <v>41</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I32" s="1">
         <v>28</v>
@@ -1360,7 +1402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D33" s="1">
         <v>29</v>
       </c>
@@ -1371,10 +1413,10 @@
         <v>29</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="4:13" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D34" s="1">
         <v>30</v>
       </c>
@@ -1388,10 +1430,10 @@
         <v>30</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="4:13" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D35" s="1">
         <v>31</v>
       </c>
@@ -1408,7 +1450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D36" s="1">
         <v>32</v>
       </c>
@@ -1416,33 +1458,33 @@
         <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I36" s="1">
         <v>32</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="4:13" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I37" s="1">
         <v>33</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I38" s="1">
         <v>34</v>
       </c>
@@ -1450,21 +1492,25 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I39" s="1">
         <v>35</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I40" s="1">
         <v>36</v>
       </c>
@@ -1472,15 +1518,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I41" s="1">
         <v>37</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="4:13" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I42" s="1">
         <v>38</v>
       </c>
@@ -1488,10 +1534,13 @@
         <v>48</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="4:13" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I43" s="1">
         <v>39</v>
       </c>
@@ -1499,7 +1548,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I44" s="1">
         <v>40</v>
       </c>
@@ -1510,13 +1559,13 @@
         <v>16</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="4:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I45" s="1">
         <v>41</v>
       </c>
@@ -1524,21 +1573,24 @@
         <v>8</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="4:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I46" s="1">
         <v>42</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="4:13" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I47" s="1">
         <v>43</v>
       </c>
@@ -1546,38 +1598,47 @@
         <v>6</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I48" s="1">
         <v>44</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="9:13" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="9:15" x14ac:dyDescent="0.3">
       <c r="I49" s="1">
         <v>45</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
